--- a/artfynd/A 28556-2026 artfynd.xlsx
+++ b/artfynd/A 28556-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134987982</v>
+        <v>135296720</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>92534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568421</v>
+        <v>568416</v>
       </c>
       <c r="R2" t="n">
-        <v>6408049</v>
+        <v>6408055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,17 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,17 +777,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134988111</v>
+        <v>135296730</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>92534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,42 +795,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trästad S skog, Sm</t>
+          <t>A 28556, Trästad, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568436</v>
+        <v>568407</v>
       </c>
       <c r="R3" t="n">
-        <v>6408081</v>
+        <v>6408031</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,34 +886,34 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134988005</v>
+        <v>134987982</v>
       </c>
       <c r="B4" t="n">
-        <v>58134</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -918,16 +921,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -943,7 +942,7 @@
         <v>6408049</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +976,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kanske fler</t>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,27 +1003,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134988051</v>
+        <v>134988111</v>
       </c>
       <c r="B5" t="n">
-        <v>58134</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1032,32 +1031,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 28556, Trästad, Sm</t>
+          <t>Trästad S skog, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568396</v>
+        <v>568436</v>
       </c>
       <c r="R5" t="n">
-        <v>6408101</v>
+        <v>6408081</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,6 +1105,338 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134988005</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 28556, Trästad, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>568421</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6408049</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kanske fler</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134988051</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 28556, Trästad, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>568396</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6408101</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135296740</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 28556, Trästad, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>568414</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6408081</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28556-2026 artfynd.xlsx
+++ b/artfynd/A 28556-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134987982</v>
+        <v>135296720</v>
       </c>
       <c r="B2" t="n">
-        <v>57977</v>
+        <v>92608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568421</v>
+        <v>568416</v>
       </c>
       <c r="R2" t="n">
-        <v>6408049</v>
+        <v>6408055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,17 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,22 +782,22 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134987982</t>
+          <t>https://artportalen.se/Sighting/135296720</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134988111</v>
+        <v>135296730</v>
       </c>
       <c r="B3" t="n">
-        <v>57977</v>
+        <v>92608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,42 +805,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trästad S skog, Sm</t>
+          <t>A 28556, Trästad, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568436</v>
+        <v>568407</v>
       </c>
       <c r="R3" t="n">
-        <v>6408081</v>
+        <v>6408031</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,39 +896,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134988111</t>
+          <t>https://artportalen.se/Sighting/135296730</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134988005</v>
+        <v>134987982</v>
       </c>
       <c r="B4" t="n">
-        <v>58139</v>
+        <v>57977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -933,16 +936,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -958,7 +957,7 @@
         <v>6408049</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,7 +991,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kanske fler</t>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,33 +1017,33 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134988005</t>
+          <t>https://artportalen.se/Sighting/134987982</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134988051</v>
+        <v>134988111</v>
       </c>
       <c r="B5" t="n">
-        <v>58139</v>
+        <v>57977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1052,32 +1051,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 28556, Trästad, Sm</t>
+          <t>Trästad S skog, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568396</v>
+        <v>568436</v>
       </c>
       <c r="R5" t="n">
-        <v>6408101</v>
+        <v>6408081</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,7 +1127,354 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134988111</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134988005</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58139</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 28556, Trästad, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>568421</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6408049</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kanske fler</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134988005</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134988051</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58139</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 28556, Trästad, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>568396</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6408101</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Susanne Hernqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134988051</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135296740</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58139</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 28556, Trästad, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>568414</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6408081</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296740</t>
         </is>
       </c>
     </row>
@@ -1142,6 +1484,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28556-2026 artfynd.xlsx
+++ b/artfynd/A 28556-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135296720</v>
       </c>
       <c r="B2" t="n">
-        <v>92608</v>
+        <v>92610</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>135296730</v>
       </c>
       <c r="B3" t="n">
-        <v>92608</v>
+        <v>92610</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
